--- a/12칸 기록지.xlsx
+++ b/12칸 기록지.xlsx
@@ -5,17 +5,17 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\User\Desktop\양식\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\User\Desktop\new\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{81C37201-B28C-48CF-8233-9CB35E73F967}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6C9E199B-A256-4090-A40B-0740E666384C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="14400" yWindow="0" windowWidth="14400" windowHeight="15600" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="교정점검표" sheetId="1" r:id="rId1"/>
   </sheets>
-  <calcPr calcId="0"/>
+  <calcPr calcId="181029"/>
 </workbook>
 </file>
 
@@ -136,18 +136,18 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <sz val="8.5"/>
+      <sz val="8.8000000000000007"/>
+      <name val="맑은 고딕"/>
+      <family val="3"/>
+      <charset val="129"/>
+    </font>
+    <font>
+      <sz val="9"/>
       <color theme="1"/>
       <name val="맑은 고딕"/>
       <family val="3"/>
       <charset val="129"/>
       <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="8.8000000000000007"/>
-      <name val="맑은 고딕"/>
-      <family val="3"/>
-      <charset val="129"/>
     </font>
   </fonts>
   <fills count="2">
@@ -300,7 +300,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="22">
+  <cellXfs count="25">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -308,12 +308,6 @@
     <xf numFmtId="0" fontId="1" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
@@ -323,6 +317,10 @@
     <xf numFmtId="0" fontId="6" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
@@ -332,20 +330,9 @@
     <xf numFmtId="0" fontId="2" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
@@ -353,13 +340,35 @@
     <xf numFmtId="0" fontId="4" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -678,42 +687,42 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:9" ht="21.95" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A1" s="18" t="s">
+      <c r="A1" s="6" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="19"/>
-      <c r="C1" s="18"/>
-      <c r="D1" s="20"/>
-      <c r="E1" s="20"/>
-      <c r="F1" s="19"/>
+      <c r="B1" s="7"/>
+      <c r="C1" s="6"/>
+      <c r="D1" s="11"/>
+      <c r="E1" s="11"/>
+      <c r="F1" s="7"/>
       <c r="G1" s="1" t="s">
         <v>10</v>
       </c>
       <c r="H1" s="1" t="s">
         <v>12</v>
       </c>
-      <c r="I1" s="7" t="s">
+      <c r="I1" s="5" t="s">
         <v>14</v>
       </c>
     </row>
     <row r="2" spans="1:9" ht="21.95" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A2" s="18" t="s">
+      <c r="A2" s="6" t="s">
         <v>1</v>
       </c>
-      <c r="B2" s="19"/>
-      <c r="C2" s="21" t="s">
+      <c r="B2" s="7"/>
+      <c r="C2" s="12" t="s">
         <v>13</v>
       </c>
-      <c r="D2" s="16"/>
-      <c r="E2" s="16"/>
-      <c r="F2" s="17"/>
+      <c r="D2" s="13"/>
+      <c r="E2" s="13"/>
+      <c r="F2" s="14"/>
       <c r="G2" s="1" t="s">
         <v>11</v>
       </c>
-      <c r="H2" s="5" t="s">
+      <c r="H2" s="3" t="s">
         <v>12</v>
       </c>
-      <c r="I2" s="6" t="s">
+      <c r="I2" s="4" t="s">
         <v>15</v>
       </c>
     </row>
@@ -747,866 +756,853 @@
       </c>
     </row>
     <row r="4" spans="1:9" ht="13.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A4" s="8"/>
-      <c r="B4" s="8"/>
-      <c r="C4" s="8"/>
-      <c r="D4" s="8"/>
-      <c r="E4" s="8"/>
+      <c r="A4" s="15"/>
+      <c r="B4" s="15"/>
+      <c r="C4" s="15"/>
+      <c r="D4" s="15"/>
+      <c r="E4" s="15"/>
       <c r="F4" s="8"/>
-      <c r="G4" s="3"/>
-      <c r="H4" s="3"/>
-      <c r="I4" s="8"/>
+      <c r="G4" s="16"/>
+      <c r="H4" s="16"/>
+      <c r="I4" s="15"/>
     </row>
     <row r="5" spans="1:9" ht="13.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A5" s="9"/>
-      <c r="B5" s="9"/>
-      <c r="C5" s="9"/>
-      <c r="D5" s="9"/>
-      <c r="E5" s="9"/>
+      <c r="A5" s="17"/>
+      <c r="B5" s="17"/>
+      <c r="C5" s="17"/>
+      <c r="D5" s="17"/>
+      <c r="E5" s="17"/>
       <c r="F5" s="9"/>
-      <c r="G5" s="3"/>
-      <c r="H5" s="3"/>
-      <c r="I5" s="9"/>
+      <c r="G5" s="16"/>
+      <c r="H5" s="16"/>
+      <c r="I5" s="17"/>
     </row>
     <row r="6" spans="1:9" ht="6.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A6" s="9"/>
-      <c r="B6" s="9"/>
-      <c r="C6" s="11"/>
-      <c r="D6" s="9"/>
-      <c r="E6" s="11"/>
+      <c r="A6" s="17"/>
+      <c r="B6" s="17"/>
+      <c r="C6" s="18"/>
+      <c r="D6" s="17"/>
+      <c r="E6" s="18"/>
       <c r="F6" s="9"/>
-      <c r="G6" s="12"/>
-      <c r="H6" s="12"/>
-      <c r="I6" s="9"/>
+      <c r="G6" s="19"/>
+      <c r="H6" s="19"/>
+      <c r="I6" s="17"/>
     </row>
     <row r="7" spans="1:9" ht="6.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A7" s="9"/>
-      <c r="B7" s="9"/>
-      <c r="C7" s="13"/>
-      <c r="D7" s="9"/>
-      <c r="E7" s="13"/>
+      <c r="A7" s="17"/>
+      <c r="B7" s="17"/>
+      <c r="C7" s="20"/>
+      <c r="D7" s="17"/>
+      <c r="E7" s="20"/>
       <c r="F7" s="9"/>
-      <c r="G7" s="11"/>
-      <c r="H7" s="11"/>
-      <c r="I7" s="9"/>
+      <c r="G7" s="18"/>
+      <c r="H7" s="18"/>
+      <c r="I7" s="17"/>
     </row>
     <row r="8" spans="1:9" ht="13.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A8" s="9"/>
-      <c r="B8" s="9"/>
-      <c r="C8" s="14"/>
-      <c r="D8" s="9"/>
-      <c r="E8" s="14"/>
+      <c r="A8" s="17"/>
+      <c r="B8" s="17"/>
+      <c r="C8" s="21"/>
+      <c r="D8" s="17"/>
+      <c r="E8" s="21"/>
       <c r="F8" s="9"/>
-      <c r="G8" s="3"/>
-      <c r="H8" s="3"/>
-      <c r="I8" s="9"/>
+      <c r="G8" s="16"/>
+      <c r="H8" s="16"/>
+      <c r="I8" s="17"/>
     </row>
     <row r="9" spans="1:9" ht="13.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A9" s="10"/>
-      <c r="B9" s="10"/>
-      <c r="C9" s="15"/>
-      <c r="D9" s="10"/>
-      <c r="E9" s="15"/>
+      <c r="A9" s="22"/>
+      <c r="B9" s="22"/>
+      <c r="C9" s="23"/>
+      <c r="D9" s="22"/>
+      <c r="E9" s="23"/>
       <c r="F9" s="10"/>
-      <c r="G9" s="4"/>
-      <c r="H9" s="4"/>
-      <c r="I9" s="10"/>
+      <c r="G9" s="24"/>
+      <c r="H9" s="24"/>
+      <c r="I9" s="22"/>
     </row>
     <row r="10" spans="1:9" ht="13.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A10" s="8"/>
-      <c r="B10" s="8"/>
-      <c r="C10" s="8"/>
-      <c r="D10" s="8"/>
-      <c r="E10" s="8"/>
+      <c r="A10" s="15"/>
+      <c r="B10" s="15"/>
+      <c r="C10" s="15"/>
+      <c r="D10" s="15"/>
+      <c r="E10" s="15"/>
       <c r="F10" s="8"/>
-      <c r="G10" s="3"/>
-      <c r="H10" s="3"/>
-      <c r="I10" s="8"/>
+      <c r="G10" s="16"/>
+      <c r="H10" s="16"/>
+      <c r="I10" s="15"/>
     </row>
     <row r="11" spans="1:9" ht="13.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A11" s="9"/>
-      <c r="B11" s="9"/>
-      <c r="C11" s="9"/>
-      <c r="D11" s="9"/>
-      <c r="E11" s="9"/>
+      <c r="A11" s="17"/>
+      <c r="B11" s="17"/>
+      <c r="C11" s="17"/>
+      <c r="D11" s="17"/>
+      <c r="E11" s="17"/>
       <c r="F11" s="9"/>
-      <c r="G11" s="3"/>
-      <c r="H11" s="3"/>
-      <c r="I11" s="9"/>
+      <c r="G11" s="16"/>
+      <c r="H11" s="16"/>
+      <c r="I11" s="17"/>
     </row>
     <row r="12" spans="1:9" ht="6.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A12" s="9"/>
-      <c r="B12" s="9"/>
-      <c r="C12" s="11"/>
-      <c r="D12" s="9"/>
-      <c r="E12" s="11"/>
+      <c r="A12" s="17"/>
+      <c r="B12" s="17"/>
+      <c r="C12" s="18"/>
+      <c r="D12" s="17"/>
+      <c r="E12" s="18"/>
       <c r="F12" s="9"/>
-      <c r="G12" s="12"/>
-      <c r="H12" s="12"/>
-      <c r="I12" s="9"/>
+      <c r="G12" s="19"/>
+      <c r="H12" s="19"/>
+      <c r="I12" s="17"/>
     </row>
     <row r="13" spans="1:9" ht="6.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A13" s="9"/>
-      <c r="B13" s="9"/>
-      <c r="C13" s="13"/>
-      <c r="D13" s="9"/>
-      <c r="E13" s="13"/>
+      <c r="A13" s="17"/>
+      <c r="B13" s="17"/>
+      <c r="C13" s="20"/>
+      <c r="D13" s="17"/>
+      <c r="E13" s="20"/>
       <c r="F13" s="9"/>
-      <c r="G13" s="11"/>
-      <c r="H13" s="11"/>
-      <c r="I13" s="9"/>
+      <c r="G13" s="18"/>
+      <c r="H13" s="18"/>
+      <c r="I13" s="17"/>
     </row>
     <row r="14" spans="1:9" ht="13.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A14" s="9"/>
-      <c r="B14" s="9"/>
-      <c r="C14" s="14"/>
-      <c r="D14" s="9"/>
-      <c r="E14" s="14"/>
+      <c r="A14" s="17"/>
+      <c r="B14" s="17"/>
+      <c r="C14" s="21"/>
+      <c r="D14" s="17"/>
+      <c r="E14" s="21"/>
       <c r="F14" s="9"/>
-      <c r="G14" s="3"/>
-      <c r="H14" s="3"/>
-      <c r="I14" s="9"/>
+      <c r="G14" s="16"/>
+      <c r="H14" s="16"/>
+      <c r="I14" s="17"/>
     </row>
     <row r="15" spans="1:9" ht="13.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A15" s="10"/>
-      <c r="B15" s="10"/>
-      <c r="C15" s="15"/>
-      <c r="D15" s="10"/>
-      <c r="E15" s="15"/>
+      <c r="A15" s="22"/>
+      <c r="B15" s="22"/>
+      <c r="C15" s="23"/>
+      <c r="D15" s="22"/>
+      <c r="E15" s="23"/>
       <c r="F15" s="10"/>
-      <c r="G15" s="4"/>
-      <c r="H15" s="4"/>
-      <c r="I15" s="10"/>
+      <c r="G15" s="24"/>
+      <c r="H15" s="24"/>
+      <c r="I15" s="22"/>
     </row>
     <row r="16" spans="1:9" ht="13.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A16" s="8"/>
-      <c r="B16" s="8"/>
-      <c r="C16" s="8"/>
-      <c r="D16" s="8"/>
-      <c r="E16" s="8"/>
+      <c r="A16" s="15"/>
+      <c r="B16" s="15"/>
+      <c r="C16" s="15"/>
+      <c r="D16" s="15"/>
+      <c r="E16" s="15"/>
       <c r="F16" s="8"/>
-      <c r="G16" s="3"/>
-      <c r="H16" s="3"/>
-      <c r="I16" s="8"/>
+      <c r="G16" s="16"/>
+      <c r="H16" s="16"/>
+      <c r="I16" s="15"/>
     </row>
     <row r="17" spans="1:9" ht="13.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A17" s="9"/>
-      <c r="B17" s="9"/>
-      <c r="C17" s="9"/>
-      <c r="D17" s="9"/>
-      <c r="E17" s="9"/>
+      <c r="A17" s="17"/>
+      <c r="B17" s="17"/>
+      <c r="C17" s="17"/>
+      <c r="D17" s="17"/>
+      <c r="E17" s="17"/>
       <c r="F17" s="9"/>
-      <c r="G17" s="3"/>
-      <c r="H17" s="3"/>
-      <c r="I17" s="9"/>
+      <c r="G17" s="16"/>
+      <c r="H17" s="16"/>
+      <c r="I17" s="17"/>
     </row>
     <row r="18" spans="1:9" ht="6.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A18" s="9"/>
-      <c r="B18" s="9"/>
-      <c r="C18" s="11"/>
-      <c r="D18" s="9"/>
-      <c r="E18" s="11"/>
+      <c r="A18" s="17"/>
+      <c r="B18" s="17"/>
+      <c r="C18" s="18"/>
+      <c r="D18" s="17"/>
+      <c r="E18" s="18"/>
       <c r="F18" s="9"/>
-      <c r="G18" s="12"/>
-      <c r="H18" s="12"/>
-      <c r="I18" s="9"/>
+      <c r="G18" s="19"/>
+      <c r="H18" s="19"/>
+      <c r="I18" s="17"/>
     </row>
     <row r="19" spans="1:9" ht="6.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A19" s="9"/>
-      <c r="B19" s="9"/>
-      <c r="C19" s="13"/>
-      <c r="D19" s="9"/>
-      <c r="E19" s="13"/>
+      <c r="A19" s="17"/>
+      <c r="B19" s="17"/>
+      <c r="C19" s="20"/>
+      <c r="D19" s="17"/>
+      <c r="E19" s="20"/>
       <c r="F19" s="9"/>
-      <c r="G19" s="11"/>
-      <c r="H19" s="11"/>
-      <c r="I19" s="9"/>
+      <c r="G19" s="18"/>
+      <c r="H19" s="18"/>
+      <c r="I19" s="17"/>
     </row>
     <row r="20" spans="1:9" ht="13.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A20" s="9"/>
-      <c r="B20" s="9"/>
-      <c r="C20" s="14"/>
-      <c r="D20" s="9"/>
-      <c r="E20" s="14"/>
+      <c r="A20" s="17"/>
+      <c r="B20" s="17"/>
+      <c r="C20" s="21"/>
+      <c r="D20" s="17"/>
+      <c r="E20" s="21"/>
       <c r="F20" s="9"/>
-      <c r="G20" s="3"/>
-      <c r="H20" s="3"/>
-      <c r="I20" s="9"/>
+      <c r="G20" s="16"/>
+      <c r="H20" s="16"/>
+      <c r="I20" s="17"/>
     </row>
     <row r="21" spans="1:9" ht="13.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A21" s="10"/>
-      <c r="B21" s="10"/>
-      <c r="C21" s="15"/>
-      <c r="D21" s="10"/>
-      <c r="E21" s="15"/>
+      <c r="A21" s="22"/>
+      <c r="B21" s="22"/>
+      <c r="C21" s="23"/>
+      <c r="D21" s="22"/>
+      <c r="E21" s="23"/>
       <c r="F21" s="10"/>
-      <c r="G21" s="4"/>
-      <c r="H21" s="4"/>
-      <c r="I21" s="10"/>
+      <c r="G21" s="24"/>
+      <c r="H21" s="24"/>
+      <c r="I21" s="22"/>
     </row>
     <row r="22" spans="1:9" ht="13.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A22" s="8"/>
-      <c r="B22" s="8"/>
-      <c r="C22" s="8"/>
-      <c r="D22" s="8"/>
-      <c r="E22" s="8"/>
+      <c r="A22" s="15"/>
+      <c r="B22" s="15"/>
+      <c r="C22" s="15"/>
+      <c r="D22" s="15"/>
+      <c r="E22" s="15"/>
       <c r="F22" s="8"/>
-      <c r="G22" s="3"/>
-      <c r="H22" s="3"/>
-      <c r="I22" s="8"/>
+      <c r="G22" s="16"/>
+      <c r="H22" s="16"/>
+      <c r="I22" s="15"/>
     </row>
     <row r="23" spans="1:9" ht="13.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A23" s="9"/>
-      <c r="B23" s="9"/>
-      <c r="C23" s="9"/>
-      <c r="D23" s="9"/>
-      <c r="E23" s="9"/>
+      <c r="A23" s="17"/>
+      <c r="B23" s="17"/>
+      <c r="C23" s="17"/>
+      <c r="D23" s="17"/>
+      <c r="E23" s="17"/>
       <c r="F23" s="9"/>
-      <c r="G23" s="3"/>
-      <c r="H23" s="3"/>
-      <c r="I23" s="9"/>
+      <c r="G23" s="16"/>
+      <c r="H23" s="16"/>
+      <c r="I23" s="17"/>
     </row>
     <row r="24" spans="1:9" ht="6.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A24" s="9"/>
-      <c r="B24" s="9"/>
-      <c r="C24" s="11"/>
-      <c r="D24" s="9"/>
-      <c r="E24" s="11"/>
+      <c r="A24" s="17"/>
+      <c r="B24" s="17"/>
+      <c r="C24" s="18"/>
+      <c r="D24" s="17"/>
+      <c r="E24" s="18"/>
       <c r="F24" s="9"/>
-      <c r="G24" s="12"/>
-      <c r="H24" s="12"/>
-      <c r="I24" s="9"/>
+      <c r="G24" s="19"/>
+      <c r="H24" s="19"/>
+      <c r="I24" s="17"/>
     </row>
     <row r="25" spans="1:9" ht="6.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A25" s="9"/>
-      <c r="B25" s="9"/>
-      <c r="C25" s="13"/>
-      <c r="D25" s="9"/>
-      <c r="E25" s="13"/>
+      <c r="A25" s="17"/>
+      <c r="B25" s="17"/>
+      <c r="C25" s="20"/>
+      <c r="D25" s="17"/>
+      <c r="E25" s="20"/>
       <c r="F25" s="9"/>
-      <c r="G25" s="11"/>
-      <c r="H25" s="11"/>
-      <c r="I25" s="9"/>
+      <c r="G25" s="18"/>
+      <c r="H25" s="18"/>
+      <c r="I25" s="17"/>
     </row>
     <row r="26" spans="1:9" ht="13.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A26" s="9"/>
-      <c r="B26" s="9"/>
-      <c r="C26" s="14"/>
-      <c r="D26" s="9"/>
-      <c r="E26" s="14"/>
+      <c r="A26" s="17"/>
+      <c r="B26" s="17"/>
+      <c r="C26" s="21"/>
+      <c r="D26" s="17"/>
+      <c r="E26" s="21"/>
       <c r="F26" s="9"/>
-      <c r="G26" s="3"/>
-      <c r="H26" s="3"/>
-      <c r="I26" s="9"/>
+      <c r="G26" s="16"/>
+      <c r="H26" s="16"/>
+      <c r="I26" s="17"/>
     </row>
     <row r="27" spans="1:9" ht="13.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A27" s="10"/>
-      <c r="B27" s="10"/>
-      <c r="C27" s="15"/>
-      <c r="D27" s="10"/>
-      <c r="E27" s="15"/>
+      <c r="A27" s="22"/>
+      <c r="B27" s="22"/>
+      <c r="C27" s="23"/>
+      <c r="D27" s="22"/>
+      <c r="E27" s="23"/>
       <c r="F27" s="10"/>
-      <c r="G27" s="4"/>
-      <c r="H27" s="4"/>
-      <c r="I27" s="10"/>
+      <c r="G27" s="24"/>
+      <c r="H27" s="24"/>
+      <c r="I27" s="22"/>
     </row>
     <row r="28" spans="1:9" ht="13.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A28" s="8"/>
-      <c r="B28" s="8"/>
-      <c r="C28" s="8"/>
-      <c r="D28" s="8"/>
-      <c r="E28" s="8"/>
+      <c r="A28" s="15"/>
+      <c r="B28" s="15"/>
+      <c r="C28" s="15"/>
+      <c r="D28" s="15"/>
+      <c r="E28" s="15"/>
       <c r="F28" s="8"/>
-      <c r="G28" s="3"/>
-      <c r="H28" s="3"/>
-      <c r="I28" s="8"/>
+      <c r="G28" s="16"/>
+      <c r="H28" s="16"/>
+      <c r="I28" s="15"/>
     </row>
     <row r="29" spans="1:9" ht="13.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A29" s="9"/>
-      <c r="B29" s="9"/>
-      <c r="C29" s="9"/>
-      <c r="D29" s="9"/>
-      <c r="E29" s="9"/>
+      <c r="A29" s="17"/>
+      <c r="B29" s="17"/>
+      <c r="C29" s="17"/>
+      <c r="D29" s="17"/>
+      <c r="E29" s="17"/>
       <c r="F29" s="9"/>
-      <c r="G29" s="3"/>
-      <c r="H29" s="3"/>
-      <c r="I29" s="9"/>
+      <c r="G29" s="16"/>
+      <c r="H29" s="16"/>
+      <c r="I29" s="17"/>
     </row>
     <row r="30" spans="1:9" ht="6.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A30" s="9"/>
-      <c r="B30" s="9"/>
-      <c r="C30" s="11"/>
-      <c r="D30" s="9"/>
-      <c r="E30" s="11"/>
+      <c r="A30" s="17"/>
+      <c r="B30" s="17"/>
+      <c r="C30" s="18"/>
+      <c r="D30" s="17"/>
+      <c r="E30" s="18"/>
       <c r="F30" s="9"/>
-      <c r="G30" s="12"/>
-      <c r="H30" s="12"/>
-      <c r="I30" s="9"/>
+      <c r="G30" s="19"/>
+      <c r="H30" s="19"/>
+      <c r="I30" s="17"/>
     </row>
     <row r="31" spans="1:9" ht="6.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A31" s="9"/>
-      <c r="B31" s="9"/>
-      <c r="C31" s="13"/>
-      <c r="D31" s="9"/>
-      <c r="E31" s="13"/>
+      <c r="A31" s="17"/>
+      <c r="B31" s="17"/>
+      <c r="C31" s="20"/>
+      <c r="D31" s="17"/>
+      <c r="E31" s="20"/>
       <c r="F31" s="9"/>
-      <c r="G31" s="11"/>
-      <c r="H31" s="11"/>
-      <c r="I31" s="9"/>
+      <c r="G31" s="18"/>
+      <c r="H31" s="18"/>
+      <c r="I31" s="17"/>
     </row>
     <row r="32" spans="1:9" ht="13.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A32" s="9"/>
-      <c r="B32" s="9"/>
-      <c r="C32" s="14"/>
-      <c r="D32" s="9"/>
-      <c r="E32" s="14"/>
+      <c r="A32" s="17"/>
+      <c r="B32" s="17"/>
+      <c r="C32" s="21"/>
+      <c r="D32" s="17"/>
+      <c r="E32" s="21"/>
       <c r="F32" s="9"/>
-      <c r="G32" s="3"/>
-      <c r="H32" s="3"/>
-      <c r="I32" s="9"/>
+      <c r="G32" s="16"/>
+      <c r="H32" s="16"/>
+      <c r="I32" s="17"/>
     </row>
     <row r="33" spans="1:9" ht="13.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A33" s="10"/>
-      <c r="B33" s="10"/>
-      <c r="C33" s="15"/>
-      <c r="D33" s="10"/>
-      <c r="E33" s="15"/>
+      <c r="A33" s="22"/>
+      <c r="B33" s="22"/>
+      <c r="C33" s="23"/>
+      <c r="D33" s="22"/>
+      <c r="E33" s="23"/>
       <c r="F33" s="10"/>
-      <c r="G33" s="4"/>
-      <c r="H33" s="4"/>
-      <c r="I33" s="10"/>
+      <c r="G33" s="24"/>
+      <c r="H33" s="24"/>
+      <c r="I33" s="22"/>
     </row>
     <row r="34" spans="1:9" ht="13.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A34" s="8"/>
-      <c r="B34" s="8"/>
-      <c r="C34" s="8"/>
-      <c r="D34" s="8"/>
-      <c r="E34" s="8"/>
+      <c r="A34" s="15"/>
+      <c r="B34" s="15"/>
+      <c r="C34" s="15"/>
+      <c r="D34" s="15"/>
+      <c r="E34" s="15"/>
       <c r="F34" s="8"/>
-      <c r="G34" s="3"/>
-      <c r="H34" s="3"/>
-      <c r="I34" s="8"/>
+      <c r="G34" s="16"/>
+      <c r="H34" s="16"/>
+      <c r="I34" s="15"/>
     </row>
     <row r="35" spans="1:9" ht="13.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A35" s="9"/>
-      <c r="B35" s="9"/>
-      <c r="C35" s="9"/>
-      <c r="D35" s="9"/>
-      <c r="E35" s="9"/>
+      <c r="A35" s="17"/>
+      <c r="B35" s="17"/>
+      <c r="C35" s="17"/>
+      <c r="D35" s="17"/>
+      <c r="E35" s="17"/>
       <c r="F35" s="9"/>
-      <c r="G35" s="3"/>
-      <c r="H35" s="3"/>
-      <c r="I35" s="9"/>
+      <c r="G35" s="16"/>
+      <c r="H35" s="16"/>
+      <c r="I35" s="17"/>
     </row>
     <row r="36" spans="1:9" ht="6.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A36" s="9"/>
-      <c r="B36" s="9"/>
-      <c r="C36" s="11"/>
-      <c r="D36" s="9"/>
-      <c r="E36" s="11"/>
+      <c r="A36" s="17"/>
+      <c r="B36" s="17"/>
+      <c r="C36" s="18"/>
+      <c r="D36" s="17"/>
+      <c r="E36" s="18"/>
       <c r="F36" s="9"/>
-      <c r="G36" s="12"/>
-      <c r="H36" s="12"/>
-      <c r="I36" s="9"/>
+      <c r="G36" s="19"/>
+      <c r="H36" s="19"/>
+      <c r="I36" s="17"/>
     </row>
     <row r="37" spans="1:9" ht="6.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A37" s="9"/>
-      <c r="B37" s="9"/>
-      <c r="C37" s="13"/>
-      <c r="D37" s="9"/>
-      <c r="E37" s="13"/>
+      <c r="A37" s="17"/>
+      <c r="B37" s="17"/>
+      <c r="C37" s="20"/>
+      <c r="D37" s="17"/>
+      <c r="E37" s="20"/>
       <c r="F37" s="9"/>
-      <c r="G37" s="11"/>
-      <c r="H37" s="11"/>
-      <c r="I37" s="9"/>
+      <c r="G37" s="18"/>
+      <c r="H37" s="18"/>
+      <c r="I37" s="17"/>
     </row>
     <row r="38" spans="1:9" ht="13.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A38" s="9"/>
-      <c r="B38" s="9"/>
-      <c r="C38" s="14"/>
-      <c r="D38" s="9"/>
-      <c r="E38" s="14"/>
+      <c r="A38" s="17"/>
+      <c r="B38" s="17"/>
+      <c r="C38" s="21"/>
+      <c r="D38" s="17"/>
+      <c r="E38" s="21"/>
       <c r="F38" s="9"/>
-      <c r="G38" s="3"/>
-      <c r="H38" s="3"/>
-      <c r="I38" s="9"/>
+      <c r="G38" s="16"/>
+      <c r="H38" s="16"/>
+      <c r="I38" s="17"/>
     </row>
     <row r="39" spans="1:9" ht="13.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A39" s="10"/>
-      <c r="B39" s="10"/>
-      <c r="C39" s="15"/>
-      <c r="D39" s="10"/>
-      <c r="E39" s="15"/>
+      <c r="A39" s="22"/>
+      <c r="B39" s="22"/>
+      <c r="C39" s="23"/>
+      <c r="D39" s="22"/>
+      <c r="E39" s="23"/>
       <c r="F39" s="10"/>
-      <c r="G39" s="4"/>
-      <c r="H39" s="4"/>
-      <c r="I39" s="10"/>
+      <c r="G39" s="24"/>
+      <c r="H39" s="24"/>
+      <c r="I39" s="22"/>
     </row>
     <row r="40" spans="1:9" ht="13.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A40" s="8"/>
-      <c r="B40" s="8"/>
-      <c r="C40" s="8"/>
-      <c r="D40" s="8"/>
-      <c r="E40" s="8"/>
+      <c r="A40" s="15"/>
+      <c r="B40" s="15"/>
+      <c r="C40" s="15"/>
+      <c r="D40" s="15"/>
+      <c r="E40" s="15"/>
       <c r="F40" s="8"/>
-      <c r="G40" s="3"/>
-      <c r="H40" s="3"/>
-      <c r="I40" s="8"/>
+      <c r="G40" s="16"/>
+      <c r="H40" s="16"/>
+      <c r="I40" s="15"/>
     </row>
     <row r="41" spans="1:9" ht="13.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A41" s="9"/>
-      <c r="B41" s="9"/>
-      <c r="C41" s="9"/>
-      <c r="D41" s="9"/>
-      <c r="E41" s="9"/>
+      <c r="A41" s="17"/>
+      <c r="B41" s="17"/>
+      <c r="C41" s="17"/>
+      <c r="D41" s="17"/>
+      <c r="E41" s="17"/>
       <c r="F41" s="9"/>
-      <c r="G41" s="3"/>
-      <c r="H41" s="3"/>
-      <c r="I41" s="9"/>
+      <c r="G41" s="16"/>
+      <c r="H41" s="16"/>
+      <c r="I41" s="17"/>
     </row>
     <row r="42" spans="1:9" ht="6.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A42" s="9"/>
-      <c r="B42" s="9"/>
-      <c r="C42" s="11"/>
-      <c r="D42" s="9"/>
-      <c r="E42" s="11"/>
+      <c r="A42" s="17"/>
+      <c r="B42" s="17"/>
+      <c r="C42" s="18"/>
+      <c r="D42" s="17"/>
+      <c r="E42" s="18"/>
       <c r="F42" s="9"/>
-      <c r="G42" s="12"/>
-      <c r="H42" s="12"/>
-      <c r="I42" s="9"/>
+      <c r="G42" s="19"/>
+      <c r="H42" s="19"/>
+      <c r="I42" s="17"/>
     </row>
     <row r="43" spans="1:9" ht="6.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A43" s="9"/>
-      <c r="B43" s="9"/>
-      <c r="C43" s="13"/>
-      <c r="D43" s="9"/>
-      <c r="E43" s="13"/>
+      <c r="A43" s="17"/>
+      <c r="B43" s="17"/>
+      <c r="C43" s="20"/>
+      <c r="D43" s="17"/>
+      <c r="E43" s="20"/>
       <c r="F43" s="9"/>
-      <c r="G43" s="11"/>
-      <c r="H43" s="11"/>
-      <c r="I43" s="9"/>
+      <c r="G43" s="18"/>
+      <c r="H43" s="18"/>
+      <c r="I43" s="17"/>
     </row>
     <row r="44" spans="1:9" ht="13.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A44" s="9"/>
-      <c r="B44" s="9"/>
-      <c r="C44" s="14"/>
-      <c r="D44" s="9"/>
-      <c r="E44" s="14"/>
+      <c r="A44" s="17"/>
+      <c r="B44" s="17"/>
+      <c r="C44" s="21"/>
+      <c r="D44" s="17"/>
+      <c r="E44" s="21"/>
       <c r="F44" s="9"/>
-      <c r="G44" s="3"/>
-      <c r="H44" s="3"/>
-      <c r="I44" s="9"/>
+      <c r="G44" s="16"/>
+      <c r="H44" s="16"/>
+      <c r="I44" s="17"/>
     </row>
     <row r="45" spans="1:9" ht="13.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A45" s="10"/>
-      <c r="B45" s="10"/>
-      <c r="C45" s="15"/>
-      <c r="D45" s="10"/>
-      <c r="E45" s="15"/>
+      <c r="A45" s="22"/>
+      <c r="B45" s="22"/>
+      <c r="C45" s="23"/>
+      <c r="D45" s="22"/>
+      <c r="E45" s="23"/>
       <c r="F45" s="10"/>
-      <c r="G45" s="4"/>
-      <c r="H45" s="4"/>
-      <c r="I45" s="10"/>
+      <c r="G45" s="24"/>
+      <c r="H45" s="24"/>
+      <c r="I45" s="22"/>
     </row>
     <row r="46" spans="1:9" ht="13.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A46" s="8"/>
-      <c r="B46" s="8"/>
-      <c r="C46" s="8"/>
-      <c r="D46" s="8"/>
-      <c r="E46" s="8"/>
+      <c r="A46" s="15"/>
+      <c r="B46" s="15"/>
+      <c r="C46" s="15"/>
+      <c r="D46" s="15"/>
+      <c r="E46" s="15"/>
       <c r="F46" s="8"/>
-      <c r="G46" s="3"/>
-      <c r="H46" s="3"/>
-      <c r="I46" s="8"/>
+      <c r="G46" s="16"/>
+      <c r="H46" s="16"/>
+      <c r="I46" s="15"/>
     </row>
     <row r="47" spans="1:9" ht="13.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A47" s="9"/>
-      <c r="B47" s="9"/>
-      <c r="C47" s="9"/>
-      <c r="D47" s="9"/>
-      <c r="E47" s="9"/>
+      <c r="A47" s="17"/>
+      <c r="B47" s="17"/>
+      <c r="C47" s="17"/>
+      <c r="D47" s="17"/>
+      <c r="E47" s="17"/>
       <c r="F47" s="9"/>
-      <c r="G47" s="3"/>
-      <c r="H47" s="3"/>
-      <c r="I47" s="9"/>
+      <c r="G47" s="16"/>
+      <c r="H47" s="16"/>
+      <c r="I47" s="17"/>
     </row>
     <row r="48" spans="1:9" ht="6.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A48" s="9"/>
-      <c r="B48" s="9"/>
-      <c r="C48" s="11"/>
-      <c r="D48" s="9"/>
-      <c r="E48" s="11"/>
+      <c r="A48" s="17"/>
+      <c r="B48" s="17"/>
+      <c r="C48" s="18"/>
+      <c r="D48" s="17"/>
+      <c r="E48" s="18"/>
       <c r="F48" s="9"/>
-      <c r="G48" s="12"/>
-      <c r="H48" s="12"/>
-      <c r="I48" s="9"/>
+      <c r="G48" s="19"/>
+      <c r="H48" s="19"/>
+      <c r="I48" s="17"/>
     </row>
     <row r="49" spans="1:9" ht="6.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A49" s="9"/>
-      <c r="B49" s="9"/>
-      <c r="C49" s="13"/>
-      <c r="D49" s="9"/>
-      <c r="E49" s="13"/>
+      <c r="A49" s="17"/>
+      <c r="B49" s="17"/>
+      <c r="C49" s="20"/>
+      <c r="D49" s="17"/>
+      <c r="E49" s="20"/>
       <c r="F49" s="9"/>
-      <c r="G49" s="11"/>
-      <c r="H49" s="11"/>
-      <c r="I49" s="9"/>
+      <c r="G49" s="18"/>
+      <c r="H49" s="18"/>
+      <c r="I49" s="17"/>
     </row>
     <row r="50" spans="1:9" ht="13.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A50" s="9"/>
-      <c r="B50" s="9"/>
-      <c r="C50" s="14"/>
-      <c r="D50" s="9"/>
-      <c r="E50" s="14"/>
+      <c r="A50" s="17"/>
+      <c r="B50" s="17"/>
+      <c r="C50" s="21"/>
+      <c r="D50" s="17"/>
+      <c r="E50" s="21"/>
       <c r="F50" s="9"/>
-      <c r="G50" s="3"/>
-      <c r="H50" s="3"/>
-      <c r="I50" s="9"/>
+      <c r="G50" s="16"/>
+      <c r="H50" s="16"/>
+      <c r="I50" s="17"/>
     </row>
     <row r="51" spans="1:9" ht="13.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A51" s="10"/>
-      <c r="B51" s="10"/>
-      <c r="C51" s="15"/>
-      <c r="D51" s="10"/>
-      <c r="E51" s="15"/>
+      <c r="A51" s="22"/>
+      <c r="B51" s="22"/>
+      <c r="C51" s="23"/>
+      <c r="D51" s="22"/>
+      <c r="E51" s="23"/>
       <c r="F51" s="10"/>
-      <c r="G51" s="4"/>
-      <c r="H51" s="4"/>
-      <c r="I51" s="10"/>
+      <c r="G51" s="24"/>
+      <c r="H51" s="24"/>
+      <c r="I51" s="22"/>
     </row>
     <row r="52" spans="1:9" ht="13.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A52" s="8"/>
-      <c r="B52" s="8"/>
-      <c r="C52" s="8"/>
-      <c r="D52" s="8"/>
-      <c r="E52" s="8"/>
+      <c r="A52" s="15"/>
+      <c r="B52" s="15"/>
+      <c r="C52" s="15"/>
+      <c r="D52" s="15"/>
+      <c r="E52" s="15"/>
       <c r="F52" s="8"/>
-      <c r="G52" s="3"/>
-      <c r="H52" s="3"/>
-      <c r="I52" s="8"/>
+      <c r="G52" s="16"/>
+      <c r="H52" s="16"/>
+      <c r="I52" s="15"/>
     </row>
     <row r="53" spans="1:9" ht="13.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A53" s="9"/>
-      <c r="B53" s="9"/>
-      <c r="C53" s="9"/>
-      <c r="D53" s="9"/>
-      <c r="E53" s="9"/>
+      <c r="A53" s="17"/>
+      <c r="B53" s="17"/>
+      <c r="C53" s="17"/>
+      <c r="D53" s="17"/>
+      <c r="E53" s="17"/>
       <c r="F53" s="9"/>
-      <c r="G53" s="3"/>
-      <c r="H53" s="3"/>
-      <c r="I53" s="9"/>
+      <c r="G53" s="16"/>
+      <c r="H53" s="16"/>
+      <c r="I53" s="17"/>
     </row>
     <row r="54" spans="1:9" ht="6.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A54" s="9"/>
-      <c r="B54" s="9"/>
-      <c r="C54" s="11"/>
-      <c r="D54" s="9"/>
-      <c r="E54" s="11"/>
+      <c r="A54" s="17"/>
+      <c r="B54" s="17"/>
+      <c r="C54" s="18"/>
+      <c r="D54" s="17"/>
+      <c r="E54" s="18"/>
       <c r="F54" s="9"/>
-      <c r="G54" s="12"/>
-      <c r="H54" s="12"/>
-      <c r="I54" s="9"/>
+      <c r="G54" s="19"/>
+      <c r="H54" s="19"/>
+      <c r="I54" s="17"/>
     </row>
     <row r="55" spans="1:9" ht="6.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A55" s="9"/>
-      <c r="B55" s="9"/>
-      <c r="C55" s="13"/>
-      <c r="D55" s="9"/>
-      <c r="E55" s="13"/>
+      <c r="A55" s="17"/>
+      <c r="B55" s="17"/>
+      <c r="C55" s="20"/>
+      <c r="D55" s="17"/>
+      <c r="E55" s="20"/>
       <c r="F55" s="9"/>
-      <c r="G55" s="11"/>
-      <c r="H55" s="11"/>
-      <c r="I55" s="9"/>
+      <c r="G55" s="18"/>
+      <c r="H55" s="18"/>
+      <c r="I55" s="17"/>
     </row>
     <row r="56" spans="1:9" ht="13.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A56" s="9"/>
-      <c r="B56" s="9"/>
-      <c r="C56" s="14"/>
-      <c r="D56" s="9"/>
-      <c r="E56" s="14"/>
+      <c r="A56" s="17"/>
+      <c r="B56" s="17"/>
+      <c r="C56" s="21"/>
+      <c r="D56" s="17"/>
+      <c r="E56" s="21"/>
       <c r="F56" s="9"/>
-      <c r="G56" s="3"/>
-      <c r="H56" s="3"/>
-      <c r="I56" s="9"/>
+      <c r="G56" s="16"/>
+      <c r="H56" s="16"/>
+      <c r="I56" s="17"/>
     </row>
     <row r="57" spans="1:9" ht="13.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A57" s="10"/>
-      <c r="B57" s="10"/>
-      <c r="C57" s="15"/>
-      <c r="D57" s="10"/>
-      <c r="E57" s="15"/>
+      <c r="A57" s="22"/>
+      <c r="B57" s="22"/>
+      <c r="C57" s="23"/>
+      <c r="D57" s="22"/>
+      <c r="E57" s="23"/>
       <c r="F57" s="10"/>
-      <c r="G57" s="4"/>
-      <c r="H57" s="4"/>
-      <c r="I57" s="10"/>
+      <c r="G57" s="24"/>
+      <c r="H57" s="24"/>
+      <c r="I57" s="22"/>
     </row>
     <row r="58" spans="1:9" ht="13.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A58" s="8"/>
-      <c r="B58" s="8"/>
-      <c r="C58" s="8"/>
-      <c r="D58" s="8"/>
-      <c r="E58" s="8"/>
+      <c r="A58" s="15"/>
+      <c r="B58" s="15"/>
+      <c r="C58" s="15"/>
+      <c r="D58" s="15"/>
+      <c r="E58" s="15"/>
       <c r="F58" s="8"/>
-      <c r="G58" s="3"/>
-      <c r="H58" s="3"/>
-      <c r="I58" s="8"/>
+      <c r="G58" s="16"/>
+      <c r="H58" s="16"/>
+      <c r="I58" s="15"/>
     </row>
     <row r="59" spans="1:9" ht="13.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A59" s="9"/>
-      <c r="B59" s="9"/>
-      <c r="C59" s="9"/>
-      <c r="D59" s="9"/>
-      <c r="E59" s="9"/>
+      <c r="A59" s="17"/>
+      <c r="B59" s="17"/>
+      <c r="C59" s="17"/>
+      <c r="D59" s="17"/>
+      <c r="E59" s="17"/>
       <c r="F59" s="9"/>
-      <c r="G59" s="3"/>
-      <c r="H59" s="3"/>
-      <c r="I59" s="9"/>
+      <c r="G59" s="16"/>
+      <c r="H59" s="16"/>
+      <c r="I59" s="17"/>
     </row>
     <row r="60" spans="1:9" ht="6.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A60" s="9"/>
-      <c r="B60" s="9"/>
-      <c r="C60" s="11"/>
-      <c r="D60" s="9"/>
-      <c r="E60" s="11"/>
+      <c r="A60" s="17"/>
+      <c r="B60" s="17"/>
+      <c r="C60" s="18"/>
+      <c r="D60" s="17"/>
+      <c r="E60" s="18"/>
       <c r="F60" s="9"/>
-      <c r="G60" s="12"/>
-      <c r="H60" s="12"/>
-      <c r="I60" s="9"/>
+      <c r="G60" s="19"/>
+      <c r="H60" s="19"/>
+      <c r="I60" s="17"/>
     </row>
     <row r="61" spans="1:9" ht="6.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A61" s="9"/>
-      <c r="B61" s="9"/>
-      <c r="C61" s="13"/>
-      <c r="D61" s="9"/>
-      <c r="E61" s="13"/>
+      <c r="A61" s="17"/>
+      <c r="B61" s="17"/>
+      <c r="C61" s="20"/>
+      <c r="D61" s="17"/>
+      <c r="E61" s="20"/>
       <c r="F61" s="9"/>
-      <c r="G61" s="11"/>
-      <c r="H61" s="11"/>
-      <c r="I61" s="9"/>
+      <c r="G61" s="18"/>
+      <c r="H61" s="18"/>
+      <c r="I61" s="17"/>
     </row>
     <row r="62" spans="1:9" ht="13.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A62" s="9"/>
-      <c r="B62" s="9"/>
-      <c r="C62" s="14"/>
-      <c r="D62" s="9"/>
-      <c r="E62" s="14"/>
+      <c r="A62" s="17"/>
+      <c r="B62" s="17"/>
+      <c r="C62" s="21"/>
+      <c r="D62" s="17"/>
+      <c r="E62" s="21"/>
       <c r="F62" s="9"/>
-      <c r="G62" s="3"/>
-      <c r="H62" s="3"/>
-      <c r="I62" s="9"/>
+      <c r="G62" s="16"/>
+      <c r="H62" s="16"/>
+      <c r="I62" s="17"/>
     </row>
     <row r="63" spans="1:9" ht="13.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A63" s="10"/>
-      <c r="B63" s="10"/>
-      <c r="C63" s="15"/>
-      <c r="D63" s="10"/>
-      <c r="E63" s="15"/>
+      <c r="A63" s="22"/>
+      <c r="B63" s="22"/>
+      <c r="C63" s="23"/>
+      <c r="D63" s="22"/>
+      <c r="E63" s="23"/>
       <c r="F63" s="10"/>
-      <c r="G63" s="4"/>
-      <c r="H63" s="4"/>
-      <c r="I63" s="10"/>
+      <c r="G63" s="24"/>
+      <c r="H63" s="24"/>
+      <c r="I63" s="22"/>
     </row>
     <row r="64" spans="1:9" ht="13.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A64" s="8"/>
-      <c r="B64" s="8"/>
-      <c r="C64" s="8"/>
-      <c r="D64" s="8"/>
-      <c r="E64" s="8"/>
+      <c r="A64" s="15"/>
+      <c r="B64" s="15"/>
+      <c r="C64" s="15"/>
+      <c r="D64" s="15"/>
+      <c r="E64" s="15"/>
       <c r="F64" s="8"/>
-      <c r="G64" s="3"/>
-      <c r="H64" s="3"/>
-      <c r="I64" s="8"/>
+      <c r="G64" s="16"/>
+      <c r="H64" s="16"/>
+      <c r="I64" s="15"/>
     </row>
     <row r="65" spans="1:9" ht="13.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A65" s="9"/>
-      <c r="B65" s="9"/>
-      <c r="C65" s="9"/>
-      <c r="D65" s="9"/>
-      <c r="E65" s="9"/>
+      <c r="A65" s="17"/>
+      <c r="B65" s="17"/>
+      <c r="C65" s="17"/>
+      <c r="D65" s="17"/>
+      <c r="E65" s="17"/>
       <c r="F65" s="9"/>
-      <c r="G65" s="3"/>
-      <c r="H65" s="3"/>
-      <c r="I65" s="9"/>
+      <c r="G65" s="16"/>
+      <c r="H65" s="16"/>
+      <c r="I65" s="17"/>
     </row>
     <row r="66" spans="1:9" ht="6.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A66" s="9"/>
-      <c r="B66" s="9"/>
-      <c r="C66" s="11"/>
-      <c r="D66" s="9"/>
-      <c r="E66" s="11"/>
+      <c r="A66" s="17"/>
+      <c r="B66" s="17"/>
+      <c r="C66" s="18"/>
+      <c r="D66" s="17"/>
+      <c r="E66" s="18"/>
       <c r="F66" s="9"/>
-      <c r="G66" s="12"/>
-      <c r="H66" s="12"/>
-      <c r="I66" s="9"/>
+      <c r="G66" s="19"/>
+      <c r="H66" s="19"/>
+      <c r="I66" s="17"/>
     </row>
     <row r="67" spans="1:9" ht="6.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A67" s="9"/>
-      <c r="B67" s="9"/>
-      <c r="C67" s="13"/>
-      <c r="D67" s="9"/>
-      <c r="E67" s="13"/>
+      <c r="A67" s="17"/>
+      <c r="B67" s="17"/>
+      <c r="C67" s="20"/>
+      <c r="D67" s="17"/>
+      <c r="E67" s="20"/>
       <c r="F67" s="9"/>
-      <c r="G67" s="11"/>
-      <c r="H67" s="11"/>
-      <c r="I67" s="9"/>
+      <c r="G67" s="18"/>
+      <c r="H67" s="18"/>
+      <c r="I67" s="17"/>
     </row>
     <row r="68" spans="1:9" ht="13.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A68" s="9"/>
-      <c r="B68" s="9"/>
-      <c r="C68" s="14"/>
-      <c r="D68" s="9"/>
-      <c r="E68" s="14"/>
+      <c r="A68" s="17"/>
+      <c r="B68" s="17"/>
+      <c r="C68" s="21"/>
+      <c r="D68" s="17"/>
+      <c r="E68" s="21"/>
       <c r="F68" s="9"/>
-      <c r="G68" s="3"/>
-      <c r="H68" s="3"/>
-      <c r="I68" s="9"/>
+      <c r="G68" s="16"/>
+      <c r="H68" s="16"/>
+      <c r="I68" s="17"/>
     </row>
     <row r="69" spans="1:9" ht="13.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A69" s="10"/>
-      <c r="B69" s="10"/>
-      <c r="C69" s="15"/>
-      <c r="D69" s="10"/>
-      <c r="E69" s="15"/>
+      <c r="A69" s="22"/>
+      <c r="B69" s="22"/>
+      <c r="C69" s="23"/>
+      <c r="D69" s="22"/>
+      <c r="E69" s="23"/>
       <c r="F69" s="10"/>
-      <c r="G69" s="4"/>
-      <c r="H69" s="4"/>
-      <c r="I69" s="10"/>
+      <c r="G69" s="24"/>
+      <c r="H69" s="24"/>
+      <c r="I69" s="22"/>
     </row>
     <row r="70" spans="1:9" ht="13.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A70" s="8"/>
-      <c r="B70" s="8"/>
-      <c r="C70" s="8"/>
-      <c r="D70" s="8"/>
-      <c r="E70" s="8"/>
+      <c r="A70" s="15"/>
+      <c r="B70" s="15"/>
+      <c r="C70" s="15"/>
+      <c r="D70" s="15"/>
+      <c r="E70" s="15"/>
       <c r="F70" s="8"/>
-      <c r="G70" s="3"/>
-      <c r="H70" s="3"/>
-      <c r="I70" s="8"/>
+      <c r="G70" s="16"/>
+      <c r="H70" s="16"/>
+      <c r="I70" s="15"/>
     </row>
     <row r="71" spans="1:9" ht="13.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A71" s="9"/>
-      <c r="B71" s="9"/>
-      <c r="C71" s="9"/>
-      <c r="D71" s="9"/>
-      <c r="E71" s="9"/>
+      <c r="A71" s="17"/>
+      <c r="B71" s="17"/>
+      <c r="C71" s="17"/>
+      <c r="D71" s="17"/>
+      <c r="E71" s="17"/>
       <c r="F71" s="9"/>
-      <c r="G71" s="3"/>
-      <c r="H71" s="3"/>
-      <c r="I71" s="9"/>
+      <c r="G71" s="16"/>
+      <c r="H71" s="16"/>
+      <c r="I71" s="17"/>
     </row>
     <row r="72" spans="1:9" ht="6.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A72" s="9"/>
-      <c r="B72" s="9"/>
-      <c r="C72" s="11"/>
-      <c r="D72" s="9"/>
-      <c r="E72" s="11"/>
+      <c r="A72" s="17"/>
+      <c r="B72" s="17"/>
+      <c r="C72" s="18"/>
+      <c r="D72" s="17"/>
+      <c r="E72" s="18"/>
       <c r="F72" s="9"/>
-      <c r="G72" s="12"/>
-      <c r="H72" s="12"/>
-      <c r="I72" s="9"/>
+      <c r="G72" s="19"/>
+      <c r="H72" s="19"/>
+      <c r="I72" s="17"/>
     </row>
     <row r="73" spans="1:9" ht="6.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A73" s="9"/>
-      <c r="B73" s="9"/>
-      <c r="C73" s="13"/>
-      <c r="D73" s="9"/>
-      <c r="E73" s="13"/>
+      <c r="A73" s="17"/>
+      <c r="B73" s="17"/>
+      <c r="C73" s="20"/>
+      <c r="D73" s="17"/>
+      <c r="E73" s="20"/>
       <c r="F73" s="9"/>
-      <c r="G73" s="11"/>
-      <c r="H73" s="11"/>
-      <c r="I73" s="9"/>
+      <c r="G73" s="18"/>
+      <c r="H73" s="18"/>
+      <c r="I73" s="17"/>
     </row>
     <row r="74" spans="1:9" ht="13.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A74" s="9"/>
-      <c r="B74" s="9"/>
-      <c r="C74" s="14"/>
-      <c r="D74" s="9"/>
-      <c r="E74" s="14"/>
+      <c r="A74" s="17"/>
+      <c r="B74" s="17"/>
+      <c r="C74" s="21"/>
+      <c r="D74" s="17"/>
+      <c r="E74" s="21"/>
       <c r="F74" s="9"/>
-      <c r="G74" s="3"/>
-      <c r="H74" s="3"/>
-      <c r="I74" s="9"/>
+      <c r="G74" s="16"/>
+      <c r="H74" s="16"/>
+      <c r="I74" s="17"/>
     </row>
     <row r="75" spans="1:9" ht="13.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A75" s="10"/>
-      <c r="B75" s="10"/>
-      <c r="C75" s="15"/>
-      <c r="D75" s="10"/>
-      <c r="E75" s="15"/>
+      <c r="A75" s="22"/>
+      <c r="B75" s="22"/>
+      <c r="C75" s="23"/>
+      <c r="D75" s="22"/>
+      <c r="E75" s="23"/>
       <c r="F75" s="10"/>
-      <c r="G75" s="4"/>
-      <c r="H75" s="4"/>
-      <c r="I75" s="10"/>
+      <c r="G75" s="24"/>
+      <c r="H75" s="24"/>
+      <c r="I75" s="22"/>
     </row>
   </sheetData>
   <mergeCells count="136">
-    <mergeCell ref="A1:B1"/>
-    <mergeCell ref="D4:D9"/>
-    <mergeCell ref="A2:B2"/>
-    <mergeCell ref="C10:C12"/>
-    <mergeCell ref="E10:E12"/>
-    <mergeCell ref="C1:F1"/>
-    <mergeCell ref="C40:C42"/>
-    <mergeCell ref="E25:E27"/>
-    <mergeCell ref="C22:C24"/>
-    <mergeCell ref="D22:D27"/>
-    <mergeCell ref="E22:E24"/>
-    <mergeCell ref="F22:F27"/>
-    <mergeCell ref="B4:B9"/>
-    <mergeCell ref="F16:F21"/>
-    <mergeCell ref="I4:I9"/>
-    <mergeCell ref="I10:I15"/>
-    <mergeCell ref="G12:G13"/>
-    <mergeCell ref="H12:H13"/>
-    <mergeCell ref="C13:C15"/>
-    <mergeCell ref="E13:E15"/>
-    <mergeCell ref="E55:E57"/>
-    <mergeCell ref="E40:E42"/>
-    <mergeCell ref="I22:I27"/>
-    <mergeCell ref="G24:G25"/>
-    <mergeCell ref="H24:H25"/>
-    <mergeCell ref="C2:F2"/>
-    <mergeCell ref="F4:F9"/>
-    <mergeCell ref="G6:G7"/>
-    <mergeCell ref="H6:H7"/>
-    <mergeCell ref="C4:C6"/>
-    <mergeCell ref="C7:C9"/>
-    <mergeCell ref="E7:E9"/>
-    <mergeCell ref="E4:E6"/>
-    <mergeCell ref="A10:A15"/>
-    <mergeCell ref="B10:B15"/>
-    <mergeCell ref="D10:D15"/>
-    <mergeCell ref="F10:F15"/>
-    <mergeCell ref="A4:A9"/>
-    <mergeCell ref="I16:I21"/>
-    <mergeCell ref="G18:G19"/>
-    <mergeCell ref="H18:H19"/>
-    <mergeCell ref="C19:C21"/>
-    <mergeCell ref="E19:E21"/>
-    <mergeCell ref="A28:A33"/>
-    <mergeCell ref="B28:B33"/>
-    <mergeCell ref="C28:C30"/>
-    <mergeCell ref="D28:D33"/>
-    <mergeCell ref="E28:E30"/>
-    <mergeCell ref="F28:F33"/>
-    <mergeCell ref="I28:I33"/>
-    <mergeCell ref="G30:G31"/>
-    <mergeCell ref="H30:H31"/>
-    <mergeCell ref="C31:C33"/>
-    <mergeCell ref="E31:E33"/>
-    <mergeCell ref="C25:C27"/>
-    <mergeCell ref="A22:A27"/>
-    <mergeCell ref="B22:B27"/>
-    <mergeCell ref="A16:A21"/>
-    <mergeCell ref="B16:B21"/>
-    <mergeCell ref="C16:C18"/>
-    <mergeCell ref="D16:D21"/>
-    <mergeCell ref="E16:E18"/>
-    <mergeCell ref="A34:A39"/>
-    <mergeCell ref="B34:B39"/>
-    <mergeCell ref="C34:C36"/>
-    <mergeCell ref="D34:D39"/>
-    <mergeCell ref="E34:E36"/>
+    <mergeCell ref="A70:A75"/>
+    <mergeCell ref="B70:B75"/>
+    <mergeCell ref="C70:C72"/>
+    <mergeCell ref="D70:D75"/>
+    <mergeCell ref="E70:E72"/>
+    <mergeCell ref="F70:F75"/>
+    <mergeCell ref="I70:I75"/>
+    <mergeCell ref="G72:G73"/>
+    <mergeCell ref="H72:H73"/>
+    <mergeCell ref="C73:C75"/>
+    <mergeCell ref="E73:E75"/>
+    <mergeCell ref="A64:A69"/>
+    <mergeCell ref="B64:B69"/>
+    <mergeCell ref="C64:C66"/>
+    <mergeCell ref="D64:D69"/>
+    <mergeCell ref="E64:E66"/>
+    <mergeCell ref="F64:F69"/>
+    <mergeCell ref="I64:I69"/>
+    <mergeCell ref="G66:G67"/>
+    <mergeCell ref="H66:H67"/>
+    <mergeCell ref="C67:C69"/>
+    <mergeCell ref="E67:E69"/>
+    <mergeCell ref="A58:A63"/>
+    <mergeCell ref="B58:B63"/>
+    <mergeCell ref="C58:C60"/>
+    <mergeCell ref="D58:D63"/>
+    <mergeCell ref="E58:E60"/>
+    <mergeCell ref="F58:F63"/>
+    <mergeCell ref="I58:I63"/>
+    <mergeCell ref="G60:G61"/>
+    <mergeCell ref="H60:H61"/>
+    <mergeCell ref="C61:C63"/>
+    <mergeCell ref="E61:E63"/>
+    <mergeCell ref="A52:A57"/>
+    <mergeCell ref="B52:B57"/>
+    <mergeCell ref="C52:C54"/>
+    <mergeCell ref="D52:D57"/>
+    <mergeCell ref="E52:E54"/>
+    <mergeCell ref="F52:F57"/>
+    <mergeCell ref="I52:I57"/>
+    <mergeCell ref="G54:G55"/>
+    <mergeCell ref="H54:H55"/>
+    <mergeCell ref="C55:C57"/>
+    <mergeCell ref="A46:A51"/>
+    <mergeCell ref="B46:B51"/>
+    <mergeCell ref="C46:C48"/>
+    <mergeCell ref="D46:D51"/>
+    <mergeCell ref="E46:E48"/>
+    <mergeCell ref="F46:F51"/>
+    <mergeCell ref="I46:I51"/>
+    <mergeCell ref="G48:G49"/>
+    <mergeCell ref="H48:H49"/>
+    <mergeCell ref="C49:C51"/>
+    <mergeCell ref="E49:E51"/>
     <mergeCell ref="F34:F39"/>
     <mergeCell ref="I34:I39"/>
     <mergeCell ref="G36:G37"/>
@@ -1622,60 +1618,73 @@
     <mergeCell ref="H42:H43"/>
     <mergeCell ref="C43:C45"/>
     <mergeCell ref="E43:E45"/>
-    <mergeCell ref="A46:A51"/>
-    <mergeCell ref="B46:B51"/>
-    <mergeCell ref="C46:C48"/>
-    <mergeCell ref="D46:D51"/>
-    <mergeCell ref="E46:E48"/>
-    <mergeCell ref="F46:F51"/>
-    <mergeCell ref="I46:I51"/>
-    <mergeCell ref="G48:G49"/>
-    <mergeCell ref="H48:H49"/>
-    <mergeCell ref="C49:C51"/>
-    <mergeCell ref="E49:E51"/>
-    <mergeCell ref="A52:A57"/>
-    <mergeCell ref="B52:B57"/>
-    <mergeCell ref="C52:C54"/>
-    <mergeCell ref="D52:D57"/>
-    <mergeCell ref="E52:E54"/>
-    <mergeCell ref="F52:F57"/>
-    <mergeCell ref="I52:I57"/>
-    <mergeCell ref="G54:G55"/>
-    <mergeCell ref="H54:H55"/>
-    <mergeCell ref="C55:C57"/>
-    <mergeCell ref="A58:A63"/>
-    <mergeCell ref="B58:B63"/>
-    <mergeCell ref="C58:C60"/>
-    <mergeCell ref="D58:D63"/>
-    <mergeCell ref="E58:E60"/>
-    <mergeCell ref="F58:F63"/>
-    <mergeCell ref="I58:I63"/>
-    <mergeCell ref="G60:G61"/>
-    <mergeCell ref="H60:H61"/>
-    <mergeCell ref="C61:C63"/>
-    <mergeCell ref="E61:E63"/>
-    <mergeCell ref="A64:A69"/>
-    <mergeCell ref="B64:B69"/>
-    <mergeCell ref="C64:C66"/>
-    <mergeCell ref="D64:D69"/>
-    <mergeCell ref="E64:E66"/>
-    <mergeCell ref="F64:F69"/>
-    <mergeCell ref="I64:I69"/>
-    <mergeCell ref="G66:G67"/>
-    <mergeCell ref="H66:H67"/>
-    <mergeCell ref="C67:C69"/>
-    <mergeCell ref="E67:E69"/>
-    <mergeCell ref="A70:A75"/>
-    <mergeCell ref="B70:B75"/>
-    <mergeCell ref="C70:C72"/>
-    <mergeCell ref="D70:D75"/>
-    <mergeCell ref="E70:E72"/>
-    <mergeCell ref="F70:F75"/>
-    <mergeCell ref="I70:I75"/>
-    <mergeCell ref="G72:G73"/>
-    <mergeCell ref="H72:H73"/>
-    <mergeCell ref="C73:C75"/>
-    <mergeCell ref="E73:E75"/>
+    <mergeCell ref="A16:A21"/>
+    <mergeCell ref="B16:B21"/>
+    <mergeCell ref="C16:C18"/>
+    <mergeCell ref="D16:D21"/>
+    <mergeCell ref="E16:E18"/>
+    <mergeCell ref="A34:A39"/>
+    <mergeCell ref="B34:B39"/>
+    <mergeCell ref="C34:C36"/>
+    <mergeCell ref="D34:D39"/>
+    <mergeCell ref="E34:E36"/>
+    <mergeCell ref="F28:F33"/>
+    <mergeCell ref="I28:I33"/>
+    <mergeCell ref="G30:G31"/>
+    <mergeCell ref="H30:H31"/>
+    <mergeCell ref="C31:C33"/>
+    <mergeCell ref="E31:E33"/>
+    <mergeCell ref="C25:C27"/>
+    <mergeCell ref="A22:A27"/>
+    <mergeCell ref="B22:B27"/>
+    <mergeCell ref="I4:I9"/>
+    <mergeCell ref="I10:I15"/>
+    <mergeCell ref="G12:G13"/>
+    <mergeCell ref="H12:H13"/>
+    <mergeCell ref="C13:C15"/>
+    <mergeCell ref="E13:E15"/>
+    <mergeCell ref="E55:E57"/>
+    <mergeCell ref="E40:E42"/>
+    <mergeCell ref="I22:I27"/>
+    <mergeCell ref="G24:G25"/>
+    <mergeCell ref="H24:H25"/>
+    <mergeCell ref="F4:F9"/>
+    <mergeCell ref="G6:G7"/>
+    <mergeCell ref="H6:H7"/>
+    <mergeCell ref="C4:C6"/>
+    <mergeCell ref="C7:C9"/>
+    <mergeCell ref="E7:E9"/>
+    <mergeCell ref="E4:E6"/>
+    <mergeCell ref="D10:D15"/>
+    <mergeCell ref="F10:F15"/>
+    <mergeCell ref="I16:I21"/>
+    <mergeCell ref="G18:G19"/>
+    <mergeCell ref="H18:H19"/>
+    <mergeCell ref="C19:C21"/>
+    <mergeCell ref="A1:B1"/>
+    <mergeCell ref="D4:D9"/>
+    <mergeCell ref="A2:B2"/>
+    <mergeCell ref="C10:C12"/>
+    <mergeCell ref="E10:E12"/>
+    <mergeCell ref="C1:F1"/>
+    <mergeCell ref="C40:C42"/>
+    <mergeCell ref="E25:E27"/>
+    <mergeCell ref="C22:C24"/>
+    <mergeCell ref="D22:D27"/>
+    <mergeCell ref="E22:E24"/>
+    <mergeCell ref="F22:F27"/>
+    <mergeCell ref="B4:B9"/>
+    <mergeCell ref="F16:F21"/>
+    <mergeCell ref="C2:F2"/>
+    <mergeCell ref="A10:A15"/>
+    <mergeCell ref="B10:B15"/>
+    <mergeCell ref="A4:A9"/>
+    <mergeCell ref="E19:E21"/>
+    <mergeCell ref="A28:A33"/>
+    <mergeCell ref="B28:B33"/>
+    <mergeCell ref="C28:C30"/>
+    <mergeCell ref="D28:D33"/>
+    <mergeCell ref="E28:E30"/>
   </mergeCells>
   <phoneticPr fontId="3" type="noConversion"/>
   <printOptions horizontalCentered="1" verticalCentered="1"/>
